--- a/Excel/Project/Freshmart/Src/FreshMart_Customers.xlsx
+++ b/Excel/Project/Freshmart/Src/FreshMart_Customers.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anudip\Desktop\Batch-3-ANP-D7361\Datasets\FreshMart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnudipCOA\Desktop\Rithiha\Excel\Project\Freshmart\Src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDBF1368-6D73-43E9-9699-98DF3617211D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08165948-028B-44FF-9BBE-48D8A3410D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{12744E2A-B81B-4B43-97B4-F1260E66F263}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{12744E2A-B81B-4B43-97B4-F1260E66F263}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6298" uniqueCount="2869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6308" uniqueCount="2870">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -8646,6 +8647,9 @@
   </si>
   <si>
     <t>radha700@gmail.com</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
 </sst>
 </file>
@@ -8668,10 +8672,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -8711,7 +8717,251 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8722,6 +8972,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB22DD0B-77A1-49AA-96FE-89CD34C1EE46}" name="Table1" displayName="Table1" ref="A1:K701" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:K701" xr:uid="{AB22DD0B-77A1-49AA-96FE-89CD34C1EE46}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{AEBA8851-91EB-4F29-BACA-1089DA44B5F2}" name="Customer_ID" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{5EE40D39-54E2-4D3A-8D77-F26164ADD85D}" name="Customer_Name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{41DDE33D-22FC-4ABC-9BDF-0B0BB89D6028}" name="Gender" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{9A2E2228-5972-4CD1-AAC7-4F98199FF157}" name="DOB" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{29C3CD44-805F-4FB3-9AFB-DBA4BE04B3E1}" name="Phone" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{0615E048-4BD4-4E9C-B84F-D0088E2B0E9A}" name="Email" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{8BF1EF82-7253-4F9F-BEEC-67314F662CF7}" name="City" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{87116D37-63CB-416A-9D1C-2AF8E91263D7}" name="State" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{325117A9-AD3A-46BF-AB5D-5F0228CC4885}" name="Region" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{DC38C0D8-6F03-40C1-964B-CE4B71300DF9}" name="Membership" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{5A7A7640-4AB5-4FDC-87CB-249F0503BE7F}" name="Registration_Date" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9042,21 +9312,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E37456-6969-446F-B816-8FFCA716E19B}">
   <dimension ref="A1:K701"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9091,7 +9361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -9126,7 +9396,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -9161,7 +9431,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -9196,7 +9466,7 @@
         <v>44349</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -9231,7 +9501,7 @@
         <v>44988</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -9266,7 +9536,7 @@
         <v>45509</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -9301,7 +9571,7 @@
         <v>43501</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>50</v>
       </c>
@@ -9336,7 +9606,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>55</v>
       </c>
@@ -9371,7 +9641,7 @@
         <v>43927</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
@@ -9406,7 +9676,7 @@
         <v>43977</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -9441,7 +9711,7 @@
         <v>44026</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>68</v>
       </c>
@@ -9476,7 +9746,7 @@
         <v>43489</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>72</v>
       </c>
@@ -9511,7 +9781,7 @@
         <v>45047</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
@@ -9546,7 +9816,7 @@
         <v>45168</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>80</v>
       </c>
@@ -9581,7 +9851,7 @@
         <v>44748</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
@@ -9616,7 +9886,7 @@
         <v>43840</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>92</v>
       </c>
@@ -9651,7 +9921,7 @@
         <v>45145</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>96</v>
       </c>
@@ -9686,7 +9956,7 @@
         <v>45617</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
@@ -9721,7 +9991,7 @@
         <v>44995</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>106</v>
       </c>
@@ -9756,7 +10026,7 @@
         <v>44406</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>111</v>
       </c>
@@ -9791,7 +10061,7 @@
         <v>44276</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>117</v>
       </c>
@@ -9826,7 +10096,7 @@
         <v>43566</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>123</v>
       </c>
@@ -9861,7 +10131,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>127</v>
       </c>
@@ -9896,7 +10166,7 @@
         <v>43928</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>132</v>
       </c>
@@ -9931,7 +10201,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>136</v>
       </c>
@@ -9966,7 +10236,7 @@
         <v>43182</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>140</v>
       </c>
@@ -10001,7 +10271,7 @@
         <v>44768</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>147</v>
       </c>
@@ -10036,7 +10306,7 @@
         <v>44067</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>151</v>
       </c>
@@ -10071,7 +10341,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>155</v>
       </c>
@@ -10106,7 +10376,7 @@
         <v>44076</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>159</v>
       </c>
@@ -10141,7 +10411,7 @@
         <v>44698</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>163</v>
       </c>
@@ -10176,7 +10446,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>167</v>
       </c>
@@ -10211,7 +10481,7 @@
         <v>45515</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>171</v>
       </c>
@@ -10246,7 +10516,7 @@
         <v>44397</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>175</v>
       </c>
@@ -10281,7 +10551,7 @@
         <v>44587</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>179</v>
       </c>
@@ -10316,7 +10586,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>184</v>
       </c>
@@ -10351,7 +10621,7 @@
         <v>44367</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>189</v>
       </c>
@@ -10386,7 +10656,7 @@
         <v>44913</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>195</v>
       </c>
@@ -10421,7 +10691,7 @@
         <v>44333</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>199</v>
       </c>
@@ -10456,7 +10726,7 @@
         <v>44898</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>203</v>
       </c>
@@ -10491,7 +10761,7 @@
         <v>43429</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>207</v>
       </c>
@@ -10526,7 +10796,7 @@
         <v>44463</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>211</v>
       </c>
@@ -10561,7 +10831,7 @@
         <v>45174</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>216</v>
       </c>
@@ -10596,7 +10866,7 @@
         <v>44439</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>220</v>
       </c>
@@ -10631,7 +10901,7 @@
         <v>45682</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>224</v>
       </c>
@@ -10666,7 +10936,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>229</v>
       </c>
@@ -10701,7 +10971,7 @@
         <v>45216</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>233</v>
       </c>
@@ -10736,7 +11006,7 @@
         <v>44409</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>237</v>
       </c>
@@ -10771,7 +11041,7 @@
         <v>44255</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>241</v>
       </c>
@@ -10806,7 +11076,7 @@
         <v>45437</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>245</v>
       </c>
@@ -10841,7 +11111,7 @@
         <v>43465</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>249</v>
       </c>
@@ -10876,7 +11146,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>253</v>
       </c>
@@ -10911,7 +11181,7 @@
         <v>43581</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>257</v>
       </c>
@@ -10946,7 +11216,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>261</v>
       </c>
@@ -10981,7 +11251,7 @@
         <v>44280</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>265</v>
       </c>
@@ -11016,7 +11286,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>269</v>
       </c>
@@ -11051,7 +11321,7 @@
         <v>43698</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>275</v>
       </c>
@@ -11086,7 +11356,7 @@
         <v>44118</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>279</v>
       </c>
@@ -11121,7 +11391,7 @@
         <v>43646</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>283</v>
       </c>
@@ -11156,7 +11426,7 @@
         <v>45547</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>287</v>
       </c>
@@ -11191,7 +11461,7 @@
         <v>44062</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>291</v>
       </c>
@@ -11226,7 +11496,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>295</v>
       </c>
@@ -11261,7 +11531,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>299</v>
       </c>
@@ -11296,7 +11566,7 @@
         <v>44490</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>303</v>
       </c>
@@ -11331,7 +11601,7 @@
         <v>43681</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>307</v>
       </c>
@@ -11366,7 +11636,7 @@
         <v>44251</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>311</v>
       </c>
@@ -11401,11 +11671,13 @@
         <v>45611</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C68" s="2" t="s">
         <v>13</v>
       </c>
@@ -11434,7 +11706,7 @@
         <v>43776</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>318</v>
       </c>
@@ -11469,7 +11741,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>322</v>
       </c>
@@ -11504,7 +11776,7 @@
         <v>43324</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>326</v>
       </c>
@@ -11539,7 +11811,7 @@
         <v>44888</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>330</v>
       </c>
@@ -11574,7 +11846,7 @@
         <v>45088</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>334</v>
       </c>
@@ -11609,7 +11881,7 @@
         <v>43935</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>338</v>
       </c>
@@ -11644,7 +11916,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>342</v>
       </c>
@@ -11679,7 +11951,7 @@
         <v>45255</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>346</v>
       </c>
@@ -11714,7 +11986,7 @@
         <v>45141</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>350</v>
       </c>
@@ -11749,7 +12021,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>354</v>
       </c>
@@ -11784,7 +12056,7 @@
         <v>43219</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>358</v>
       </c>
@@ -11819,7 +12091,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>362</v>
       </c>
@@ -11854,7 +12126,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>366</v>
       </c>
@@ -11889,7 +12161,7 @@
         <v>45737</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>370</v>
       </c>
@@ -11924,7 +12196,7 @@
         <v>45567</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>374</v>
       </c>
@@ -11959,7 +12231,7 @@
         <v>43466</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>378</v>
       </c>
@@ -11994,7 +12266,7 @@
         <v>45751</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>383</v>
       </c>
@@ -12029,7 +12301,7 @@
         <v>44371</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>389</v>
       </c>
@@ -12064,7 +12336,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>393</v>
       </c>
@@ -12099,7 +12371,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>397</v>
       </c>
@@ -12134,7 +12406,7 @@
         <v>44879</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>401</v>
       </c>
@@ -12169,7 +12441,7 @@
         <v>45871</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>405</v>
       </c>
@@ -12204,7 +12476,7 @@
         <v>45679</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>409</v>
       </c>
@@ -12239,7 +12511,7 @@
         <v>45057</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>413</v>
       </c>
@@ -12274,7 +12546,7 @@
         <v>44119</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>417</v>
       </c>
@@ -12309,7 +12581,7 @@
         <v>43285</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>421</v>
       </c>
@@ -12344,7 +12616,7 @@
         <v>45807</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>425</v>
       </c>
@@ -12379,7 +12651,7 @@
         <v>43435</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>429</v>
       </c>
@@ -12414,7 +12686,7 @@
         <v>43836</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>433</v>
       </c>
@@ -12449,7 +12721,7 @@
         <v>45986</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>437</v>
       </c>
@@ -12484,7 +12756,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>441</v>
       </c>
@@ -12519,7 +12791,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>445</v>
       </c>
@@ -12554,7 +12826,7 @@
         <v>44718</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>449</v>
       </c>
@@ -12589,7 +12861,7 @@
         <v>45795</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>453</v>
       </c>
@@ -12624,7 +12896,7 @@
         <v>45929</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>457</v>
       </c>
@@ -12659,7 +12931,7 @@
         <v>43613</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>461</v>
       </c>
@@ -12694,7 +12966,7 @@
         <v>43210</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>465</v>
       </c>
@@ -12729,7 +13001,7 @@
         <v>45665</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>469</v>
       </c>
@@ -12764,7 +13036,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>473</v>
       </c>
@@ -12799,7 +13071,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>477</v>
       </c>
@@ -12834,7 +13106,7 @@
         <v>44094</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>481</v>
       </c>
@@ -12869,7 +13141,7 @@
         <v>43521</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>485</v>
       </c>
@@ -12904,7 +13176,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>489</v>
       </c>
@@ -12939,7 +13211,7 @@
         <v>45092</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>493</v>
       </c>
@@ -12974,7 +13246,7 @@
         <v>44050</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>497</v>
       </c>
@@ -13009,7 +13281,7 @@
         <v>45367</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>501</v>
       </c>
@@ -13044,7 +13316,7 @@
         <v>45127</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>505</v>
       </c>
@@ -13079,7 +13351,7 @@
         <v>43761</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>511</v>
       </c>
@@ -13114,7 +13386,7 @@
         <v>45180</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>515</v>
       </c>
@@ -13149,7 +13421,7 @@
         <v>43638</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>519</v>
       </c>
@@ -13184,7 +13456,7 @@
         <v>45035</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>523</v>
       </c>
@@ -13219,7 +13491,7 @@
         <v>45833</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>528</v>
       </c>
@@ -13254,7 +13526,7 @@
         <v>43514</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>532</v>
       </c>
@@ -13289,7 +13561,7 @@
         <v>45381</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>536</v>
       </c>
@@ -13324,7 +13596,7 @@
         <v>43816</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>541</v>
       </c>
@@ -13359,7 +13631,7 @@
         <v>44864</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>545</v>
       </c>
@@ -13394,7 +13666,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>549</v>
       </c>
@@ -13429,7 +13701,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>553</v>
       </c>
@@ -13464,7 +13736,7 @@
         <v>44973</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>557</v>
       </c>
@@ -13499,7 +13771,7 @@
         <v>45404</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>561</v>
       </c>
@@ -13534,7 +13806,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>565</v>
       </c>
@@ -13569,7 +13841,7 @@
         <v>43507</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>569</v>
       </c>
@@ -13604,7 +13876,7 @@
         <v>43927</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>573</v>
       </c>
@@ -13639,7 +13911,7 @@
         <v>44499</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>578</v>
       </c>
@@ -13674,7 +13946,7 @@
         <v>44578</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>582</v>
       </c>
@@ -13709,7 +13981,7 @@
         <v>44828</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>586</v>
       </c>
@@ -13744,7 +14016,7 @@
         <v>44980</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>590</v>
       </c>
@@ -13779,7 +14051,7 @@
         <v>43697</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>594</v>
       </c>
@@ -13814,7 +14086,7 @@
         <v>44486</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -13849,7 +14121,7 @@
         <v>43252</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>602</v>
       </c>
@@ -13884,7 +14156,7 @@
         <v>44312</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>606</v>
       </c>
@@ -13919,7 +14191,7 @@
         <v>44510</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>610</v>
       </c>
@@ -13954,7 +14226,7 @@
         <v>45969</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>614</v>
       </c>
@@ -13989,7 +14261,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>618</v>
       </c>
@@ -14024,7 +14296,7 @@
         <v>43446</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>622</v>
       </c>
@@ -14059,7 +14331,7 @@
         <v>45232</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>626</v>
       </c>
@@ -14094,7 +14366,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>630</v>
       </c>
@@ -14129,7 +14401,7 @@
         <v>45527</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>634</v>
       </c>
@@ -14164,7 +14436,7 @@
         <v>43553</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>638</v>
       </c>
@@ -14199,7 +14471,7 @@
         <v>44552</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>642</v>
       </c>
@@ -14234,7 +14506,7 @@
         <v>43122</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>646</v>
       </c>
@@ -14269,7 +14541,7 @@
         <v>45417</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>650</v>
       </c>
@@ -14304,7 +14576,7 @@
         <v>45832</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>654</v>
       </c>
@@ -14339,7 +14611,7 @@
         <v>45229</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>658</v>
       </c>
@@ -14374,7 +14646,7 @@
         <v>44580</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>662</v>
       </c>
@@ -14409,7 +14681,7 @@
         <v>43478</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>666</v>
       </c>
@@ -14444,7 +14716,7 @@
         <v>43420</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>670</v>
       </c>
@@ -14479,7 +14751,7 @@
         <v>44718</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>674</v>
       </c>
@@ -14514,7 +14786,7 @@
         <v>44808</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>678</v>
       </c>
@@ -14549,7 +14821,7 @@
         <v>43630</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>682</v>
       </c>
@@ -14584,7 +14856,7 @@
         <v>44966</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>686</v>
       </c>
@@ -14619,7 +14891,7 @@
         <v>43587</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>690</v>
       </c>
@@ -14654,7 +14926,7 @@
         <v>43265</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>694</v>
       </c>
@@ -14689,7 +14961,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>698</v>
       </c>
@@ -14724,7 +14996,7 @@
         <v>44828</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>702</v>
       </c>
@@ -14759,7 +15031,7 @@
         <v>43109</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>706</v>
       </c>
@@ -14794,7 +15066,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>710</v>
       </c>
@@ -14829,7 +15101,7 @@
         <v>45047</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>714</v>
       </c>
@@ -14864,7 +15136,7 @@
         <v>45168</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>718</v>
       </c>
@@ -14899,7 +15171,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>722</v>
       </c>
@@ -14934,7 +15206,7 @@
         <v>44687</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>726</v>
       </c>
@@ -14969,7 +15241,7 @@
         <v>44237</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>730</v>
       </c>
@@ -15004,7 +15276,7 @@
         <v>45681</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>734</v>
       </c>
@@ -15039,7 +15311,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>738</v>
       </c>
@@ -15074,7 +15346,7 @@
         <v>45436</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>742</v>
       </c>
@@ -15109,7 +15381,7 @@
         <v>43593</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>746</v>
       </c>
@@ -15144,7 +15416,7 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>750</v>
       </c>
@@ -15179,7 +15451,7 @@
         <v>45586</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>754</v>
       </c>
@@ -15214,7 +15486,7 @@
         <v>44493</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>758</v>
       </c>
@@ -15249,7 +15521,7 @@
         <v>44665</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>762</v>
       </c>
@@ -15284,7 +15556,7 @@
         <v>43690</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>766</v>
       </c>
@@ -15319,7 +15591,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>770</v>
       </c>
@@ -15354,7 +15626,7 @@
         <v>44321</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>774</v>
       </c>
@@ -15389,7 +15661,7 @@
         <v>44157</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>778</v>
       </c>
@@ -15424,7 +15696,7 @@
         <v>44069</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>782</v>
       </c>
@@ -15459,7 +15731,7 @@
         <v>44204</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>786</v>
       </c>
@@ -15494,7 +15766,7 @@
         <v>43219</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>790</v>
       </c>
@@ -15529,7 +15801,7 @@
         <v>45866</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>794</v>
       </c>
@@ -15564,7 +15836,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>798</v>
       </c>
@@ -15599,7 +15871,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>802</v>
       </c>
@@ -15634,7 +15906,7 @@
         <v>45302</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>806</v>
       </c>
@@ -15669,11 +15941,13 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B190" s="2"/>
+      <c r="B190" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C190" s="2" t="s">
         <v>13</v>
       </c>
@@ -15702,7 +15976,7 @@
         <v>44220</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>813</v>
       </c>
@@ -15737,7 +16011,7 @@
         <v>45497</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>817</v>
       </c>
@@ -15772,7 +16046,7 @@
         <v>43387</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>821</v>
       </c>
@@ -15807,7 +16081,7 @@
         <v>44245</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>825</v>
       </c>
@@ -15842,7 +16116,7 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>829</v>
       </c>
@@ -15877,7 +16151,7 @@
         <v>44500</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>833</v>
       </c>
@@ -15912,7 +16186,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>837</v>
       </c>
@@ -15947,7 +16221,7 @@
         <v>44793</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>841</v>
       </c>
@@ -15982,7 +16256,7 @@
         <v>43433</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>845</v>
       </c>
@@ -16017,7 +16291,7 @@
         <v>45854</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>849</v>
       </c>
@@ -16052,7 +16326,7 @@
         <v>44685</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>853</v>
       </c>
@@ -16087,7 +16361,7 @@
         <v>43891</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>857</v>
       </c>
@@ -16122,7 +16396,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>861</v>
       </c>
@@ -16157,7 +16431,7 @@
         <v>44060</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>865</v>
       </c>
@@ -16192,7 +16466,7 @@
         <v>43130</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>869</v>
       </c>
@@ -16227,7 +16501,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>873</v>
       </c>
@@ -16262,7 +16536,7 @@
         <v>45854</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>877</v>
       </c>
@@ -16297,7 +16571,7 @@
         <v>43367</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>881</v>
       </c>
@@ -16332,7 +16606,7 @@
         <v>44224</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>885</v>
       </c>
@@ -16367,7 +16641,7 @@
         <v>45617</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>889</v>
       </c>
@@ -16402,7 +16676,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>893</v>
       </c>
@@ -16437,7 +16711,7 @@
         <v>44223</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>897</v>
       </c>
@@ -16472,7 +16746,7 @@
         <v>43279</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>901</v>
       </c>
@@ -16507,7 +16781,7 @@
         <v>44939</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>905</v>
       </c>
@@ -16542,7 +16816,7 @@
         <v>43204</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>909</v>
       </c>
@@ -16577,7 +16851,7 @@
         <v>43907</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>913</v>
       </c>
@@ -16612,7 +16886,7 @@
         <v>43215</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>917</v>
       </c>
@@ -16647,7 +16921,7 @@
         <v>44126</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>921</v>
       </c>
@@ -16682,7 +16956,7 @@
         <v>44467</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>925</v>
       </c>
@@ -16717,7 +16991,7 @@
         <v>43492</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>929</v>
       </c>
@@ -16752,7 +17026,7 @@
         <v>43237</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>934</v>
       </c>
@@ -16787,7 +17061,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>938</v>
       </c>
@@ -16822,7 +17096,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>942</v>
       </c>
@@ -16857,7 +17131,7 @@
         <v>44055</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>946</v>
       </c>
@@ -16892,7 +17166,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>950</v>
       </c>
@@ -16927,7 +17201,7 @@
         <v>45767</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>954</v>
       </c>
@@ -16962,7 +17236,7 @@
         <v>43889</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>958</v>
       </c>
@@ -16997,11 +17271,13 @@
         <v>45448</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="B228" s="2"/>
+      <c r="B228" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C228" s="2" t="s">
         <v>13</v>
       </c>
@@ -17030,7 +17306,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>965</v>
       </c>
@@ -17065,7 +17341,7 @@
         <v>43348</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>969</v>
       </c>
@@ -17100,7 +17376,7 @@
         <v>44375</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>973</v>
       </c>
@@ -17135,7 +17411,7 @@
         <v>44293</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>977</v>
       </c>
@@ -17170,7 +17446,7 @@
         <v>45392</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>981</v>
       </c>
@@ -17205,7 +17481,7 @@
         <v>43381</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>985</v>
       </c>
@@ -17240,7 +17516,7 @@
         <v>45557</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>989</v>
       </c>
@@ -17275,7 +17551,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>993</v>
       </c>
@@ -17310,7 +17586,7 @@
         <v>45132</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>997</v>
       </c>
@@ -17345,7 +17621,7 @@
         <v>45656</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>1001</v>
       </c>
@@ -17380,7 +17656,7 @@
         <v>43941</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>1005</v>
       </c>
@@ -17415,7 +17691,7 @@
         <v>44566</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>1009</v>
       </c>
@@ -17450,7 +17726,7 @@
         <v>45686</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>1013</v>
       </c>
@@ -17485,7 +17761,7 @@
         <v>43911</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>1017</v>
       </c>
@@ -17520,11 +17796,13 @@
         <v>45372</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="B243" s="2"/>
+      <c r="B243" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C243" s="2" t="s">
         <v>13</v>
       </c>
@@ -17553,7 +17831,7 @@
         <v>43515</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>1024</v>
       </c>
@@ -17588,7 +17866,7 @@
         <v>44487</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>1028</v>
       </c>
@@ -17623,7 +17901,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>1032</v>
       </c>
@@ -17658,7 +17936,7 @@
         <v>43586</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>1036</v>
       </c>
@@ -17693,7 +17971,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>1040</v>
       </c>
@@ -17728,7 +18006,7 @@
         <v>43290</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>1044</v>
       </c>
@@ -17763,7 +18041,7 @@
         <v>43709</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>1048</v>
       </c>
@@ -17798,7 +18076,7 @@
         <v>45493</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>1052</v>
       </c>
@@ -17833,7 +18111,7 @@
         <v>43786</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>1056</v>
       </c>
@@ -17868,7 +18146,7 @@
         <v>45002</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>1060</v>
       </c>
@@ -17903,7 +18181,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>1064</v>
       </c>
@@ -17938,7 +18216,7 @@
         <v>45762</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>1068</v>
       </c>
@@ -17973,7 +18251,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>1072</v>
       </c>
@@ -18008,7 +18286,7 @@
         <v>44143</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>1076</v>
       </c>
@@ -18043,7 +18321,7 @@
         <v>44541</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>1080</v>
       </c>
@@ -18078,7 +18356,7 @@
         <v>44846</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>1084</v>
       </c>
@@ -18113,7 +18391,7 @@
         <v>44399</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>1089</v>
       </c>
@@ -18148,7 +18426,7 @@
         <v>45744</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>1093</v>
       </c>
@@ -18183,7 +18461,7 @@
         <v>45201</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>1097</v>
       </c>
@@ -18218,7 +18496,7 @@
         <v>43586</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>1101</v>
       </c>
@@ -18253,7 +18531,7 @@
         <v>45866</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>1105</v>
       </c>
@@ -18288,7 +18566,7 @@
         <v>46034</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>1109</v>
       </c>
@@ -18323,7 +18601,7 @@
         <v>44255</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>1113</v>
       </c>
@@ -18358,7 +18636,7 @@
         <v>45785</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>1117</v>
       </c>
@@ -18393,7 +18671,7 @@
         <v>44729</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>1121</v>
       </c>
@@ -18428,7 +18706,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>1125</v>
       </c>
@@ -18463,7 +18741,7 @@
         <v>44496</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>1129</v>
       </c>
@@ -18498,7 +18776,7 @@
         <v>43959</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>1133</v>
       </c>
@@ -18533,7 +18811,7 @@
         <v>45466</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>1137</v>
       </c>
@@ -18568,7 +18846,7 @@
         <v>44492</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>1142</v>
       </c>
@@ -18603,7 +18881,7 @@
         <v>44328</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>1146</v>
       </c>
@@ -18638,7 +18916,7 @@
         <v>43730</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>1151</v>
       </c>
@@ -18673,7 +18951,7 @@
         <v>44702</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>1155</v>
       </c>
@@ -18708,7 +18986,7 @@
         <v>43872</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>1159</v>
       </c>
@@ -18743,7 +19021,7 @@
         <v>43482</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>1163</v>
       </c>
@@ -18778,7 +19056,7 @@
         <v>43210</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>1167</v>
       </c>
@@ -18813,7 +19091,7 @@
         <v>44293</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>1171</v>
       </c>
@@ -18848,7 +19126,7 @@
         <v>43146</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>1175</v>
       </c>
@@ -18883,7 +19161,7 @@
         <v>43629</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>1179</v>
       </c>
@@ -18918,7 +19196,7 @@
         <v>43633</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>1183</v>
       </c>
@@ -18953,7 +19231,7 @@
         <v>44372</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>1187</v>
       </c>
@@ -18988,7 +19266,7 @@
         <v>43685</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>1192</v>
       </c>
@@ -19023,7 +19301,7 @@
         <v>45254</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>1196</v>
       </c>
@@ -19058,7 +19336,7 @@
         <v>43474</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>1200</v>
       </c>
@@ -19093,7 +19371,7 @@
         <v>44702</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>1204</v>
       </c>
@@ -19128,7 +19406,7 @@
         <v>45631</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>1208</v>
       </c>
@@ -19163,7 +19441,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>1212</v>
       </c>
@@ -19198,7 +19476,7 @@
         <v>44222</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>1216</v>
       </c>
@@ -19233,7 +19511,7 @@
         <v>45122</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>1220</v>
       </c>
@@ -19268,7 +19546,7 @@
         <v>43531</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>1224</v>
       </c>
@@ -19303,7 +19581,7 @@
         <v>44136</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>1228</v>
       </c>
@@ -19336,7 +19614,7 @@
         <v>44662</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>1232</v>
       </c>
@@ -19371,7 +19649,7 @@
         <v>44127</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>1236</v>
       </c>
@@ -19406,7 +19684,7 @@
         <v>45086</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>1240</v>
       </c>
@@ -19441,7 +19719,7 @@
         <v>43675</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>1244</v>
       </c>
@@ -19476,7 +19754,7 @@
         <v>45587</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>1248</v>
       </c>
@@ -19511,7 +19789,7 @@
         <v>43790</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>1252</v>
       </c>
@@ -19546,7 +19824,7 @@
         <v>44905</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>1256</v>
       </c>
@@ -19581,7 +19859,7 @@
         <v>43986</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>1260</v>
       </c>
@@ -19616,7 +19894,7 @@
         <v>44700</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>1264</v>
       </c>
@@ -19651,7 +19929,7 @@
         <v>44646</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>1268</v>
       </c>
@@ -19686,11 +19964,13 @@
         <v>43920</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>1272</v>
       </c>
-      <c r="B305" s="2"/>
+      <c r="B305" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C305" s="2" t="s">
         <v>13</v>
       </c>
@@ -19719,7 +19999,7 @@
         <v>43888</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>1275</v>
       </c>
@@ -19754,7 +20034,7 @@
         <v>45821</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>1279</v>
       </c>
@@ -19789,7 +20069,7 @@
         <v>44440</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>1283</v>
       </c>
@@ -19824,7 +20104,7 @@
         <v>44719</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>1287</v>
       </c>
@@ -19859,7 +20139,7 @@
         <v>43812</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>1291</v>
       </c>
@@ -19894,7 +20174,7 @@
         <v>44980</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>1295</v>
       </c>
@@ -19929,7 +20209,7 @@
         <v>43280</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>1299</v>
       </c>
@@ -19964,7 +20244,7 @@
         <v>43518</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>1303</v>
       </c>
@@ -19999,7 +20279,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>1307</v>
       </c>
@@ -20034,7 +20314,7 @@
         <v>44461</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>1311</v>
       </c>
@@ -20069,7 +20349,7 @@
         <v>43377</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>1315</v>
       </c>
@@ -20104,7 +20384,7 @@
         <v>45724</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>1319</v>
       </c>
@@ -20139,7 +20419,7 @@
         <v>44053</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>1323</v>
       </c>
@@ -20174,7 +20454,7 @@
         <v>44098</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>1327</v>
       </c>
@@ -20209,7 +20489,7 @@
         <v>43928</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>1331</v>
       </c>
@@ -20244,7 +20524,7 @@
         <v>44447</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>1335</v>
       </c>
@@ -20279,7 +20559,7 @@
         <v>45755</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>1339</v>
       </c>
@@ -20314,7 +20594,7 @@
         <v>44504</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>1343</v>
       </c>
@@ -20349,7 +20629,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>1347</v>
       </c>
@@ -20384,7 +20664,7 @@
         <v>44418</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>1351</v>
       </c>
@@ -20419,7 +20699,7 @@
         <v>43387</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>1355</v>
       </c>
@@ -20454,7 +20734,7 @@
         <v>43476</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>1359</v>
       </c>
@@ -20489,7 +20769,7 @@
         <v>44846</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>1363</v>
       </c>
@@ -20524,7 +20804,7 @@
         <v>44837</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>1367</v>
       </c>
@@ -20559,7 +20839,7 @@
         <v>45704</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>1371</v>
       </c>
@@ -20594,7 +20874,7 @@
         <v>44732</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>1375</v>
       </c>
@@ -20629,7 +20909,7 @@
         <v>43739</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>1379</v>
       </c>
@@ -20664,7 +20944,7 @@
         <v>43441</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>1383</v>
       </c>
@@ -20699,7 +20979,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>1387</v>
       </c>
@@ -20734,7 +21014,7 @@
         <v>44637</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>1391</v>
       </c>
@@ -20769,7 +21049,7 @@
         <v>43902</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>1395</v>
       </c>
@@ -20804,7 +21084,7 @@
         <v>45113</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>1399</v>
       </c>
@@ -20839,7 +21119,7 @@
         <v>45726</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>1403</v>
       </c>
@@ -20874,7 +21154,7 @@
         <v>44677</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>1407</v>
       </c>
@@ -20909,7 +21189,7 @@
         <v>45188</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>1411</v>
       </c>
@@ -20944,7 +21224,7 @@
         <v>44837</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>1415</v>
       </c>
@@ -20979,7 +21259,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>1419</v>
       </c>
@@ -21014,7 +21294,7 @@
         <v>45890</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>1423</v>
       </c>
@@ -21049,7 +21329,7 @@
         <v>43151</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>1427</v>
       </c>
@@ -21084,7 +21364,7 @@
         <v>43430</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>1431</v>
       </c>
@@ -21119,7 +21399,7 @@
         <v>45934</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>1435</v>
       </c>
@@ -21154,7 +21434,7 @@
         <v>45501</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>1439</v>
       </c>
@@ -21189,7 +21469,7 @@
         <v>44511</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>1443</v>
       </c>
@@ -21224,7 +21504,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>1447</v>
       </c>
@@ -21259,7 +21539,7 @@
         <v>43497</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>1451</v>
       </c>
@@ -21294,7 +21574,7 @@
         <v>44866</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>1455</v>
       </c>
@@ -21329,7 +21609,7 @@
         <v>45093</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>1459</v>
       </c>
@@ -21364,7 +21644,7 @@
         <v>43861</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>1463</v>
       </c>
@@ -21399,7 +21679,7 @@
         <v>44163</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>1467</v>
       </c>
@@ -21434,7 +21714,7 @@
         <v>43427</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>1471</v>
       </c>
@@ -21469,7 +21749,7 @@
         <v>43222</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>1475</v>
       </c>
@@ -21504,7 +21784,7 @@
         <v>43139</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>1479</v>
       </c>
@@ -21539,7 +21819,7 @@
         <v>43497</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>1483</v>
       </c>
@@ -21574,11 +21854,13 @@
         <v>44189</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>1487</v>
       </c>
-      <c r="B359" s="2"/>
+      <c r="B359" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C359" s="2" t="s">
         <v>13</v>
       </c>
@@ -21607,7 +21889,7 @@
         <v>44619</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>1490</v>
       </c>
@@ -21642,7 +21924,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>1494</v>
       </c>
@@ -21677,7 +21959,7 @@
         <v>43113</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>1498</v>
       </c>
@@ -21712,7 +21994,7 @@
         <v>45274</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>1502</v>
       </c>
@@ -21747,7 +22029,7 @@
         <v>45210</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>1506</v>
       </c>
@@ -21782,7 +22064,7 @@
         <v>43169</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>1510</v>
       </c>
@@ -21817,7 +22099,7 @@
         <v>45877</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>1514</v>
       </c>
@@ -21852,7 +22134,7 @@
         <v>44527</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>1518</v>
       </c>
@@ -21887,7 +22169,7 @@
         <v>45587</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>1522</v>
       </c>
@@ -21922,7 +22204,7 @@
         <v>43231</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>1526</v>
       </c>
@@ -21957,7 +22239,7 @@
         <v>45013</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>1530</v>
       </c>
@@ -21992,7 +22274,7 @@
         <v>44097</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>1534</v>
       </c>
@@ -22027,7 +22309,7 @@
         <v>43757</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>1538</v>
       </c>
@@ -22062,7 +22344,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>1542</v>
       </c>
@@ -22097,7 +22379,7 @@
         <v>43471</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>1546</v>
       </c>
@@ -22132,7 +22414,7 @@
         <v>45738</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>1550</v>
       </c>
@@ -22167,7 +22449,7 @@
         <v>44890</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>1554</v>
       </c>
@@ -22202,7 +22484,7 @@
         <v>43557</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>1559</v>
       </c>
@@ -22237,7 +22519,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>1563</v>
       </c>
@@ -22272,7 +22554,7 @@
         <v>43107</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>1567</v>
       </c>
@@ -22307,7 +22589,7 @@
         <v>44836</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>1571</v>
       </c>
@@ -22342,7 +22624,7 @@
         <v>43537</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>1575</v>
       </c>
@@ -22377,7 +22659,7 @@
         <v>43997</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>1579</v>
       </c>
@@ -22412,7 +22694,7 @@
         <v>45826</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>1583</v>
       </c>
@@ -22447,7 +22729,7 @@
         <v>45158</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>1587</v>
       </c>
@@ -22482,7 +22764,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>1591</v>
       </c>
@@ -22517,7 +22799,7 @@
         <v>43726</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>1595</v>
       </c>
@@ -22552,7 +22834,7 @@
         <v>43834</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>1599</v>
       </c>
@@ -22587,7 +22869,7 @@
         <v>43189</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>1603</v>
       </c>
@@ -22622,7 +22904,7 @@
         <v>44704</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>1607</v>
       </c>
@@ -22657,7 +22939,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>1611</v>
       </c>
@@ -22692,7 +22974,7 @@
         <v>43322</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>1615</v>
       </c>
@@ -22727,7 +23009,7 @@
         <v>45951</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>1619</v>
       </c>
@@ -22762,7 +23044,7 @@
         <v>45768</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>1623</v>
       </c>
@@ -22797,7 +23079,7 @@
         <v>44643</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>1627</v>
       </c>
@@ -22832,7 +23114,7 @@
         <v>44557</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>1631</v>
       </c>
@@ -22867,7 +23149,7 @@
         <v>45763</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>1635</v>
       </c>
@@ -22902,7 +23184,7 @@
         <v>44104</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>1639</v>
       </c>
@@ -22937,7 +23219,7 @@
         <v>45774</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>1643</v>
       </c>
@@ -22972,7 +23254,7 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>1647</v>
       </c>
@@ -23007,7 +23289,7 @@
         <v>43439</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>1651</v>
       </c>
@@ -23042,7 +23324,7 @@
         <v>45447</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>1655</v>
       </c>
@@ -23077,7 +23359,7 @@
         <v>44673</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>1659</v>
       </c>
@@ -23112,7 +23394,7 @@
         <v>43508</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>1663</v>
       </c>
@@ -23147,7 +23429,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>1667</v>
       </c>
@@ -23182,7 +23464,7 @@
         <v>45496</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>1671</v>
       </c>
@@ -23217,7 +23499,7 @@
         <v>45798</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>1675</v>
       </c>
@@ -23252,7 +23534,7 @@
         <v>45373</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>1679</v>
       </c>
@@ -23287,7 +23569,7 @@
         <v>43945</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>1683</v>
       </c>
@@ -23322,7 +23604,7 @@
         <v>43447</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>1687</v>
       </c>
@@ -23357,7 +23639,7 @@
         <v>44833</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>1691</v>
       </c>
@@ -23392,7 +23674,7 @@
         <v>44302</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>1695</v>
       </c>
@@ -23427,7 +23709,7 @@
         <v>45241</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>1699</v>
       </c>
@@ -23462,7 +23744,7 @@
         <v>45815</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>1703</v>
       </c>
@@ -23497,7 +23779,7 @@
         <v>43982</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>1707</v>
       </c>
@@ -23532,7 +23814,7 @@
         <v>43627</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>1711</v>
       </c>
@@ -23567,7 +23849,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>1715</v>
       </c>
@@ -23602,7 +23884,7 @@
         <v>45872</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>1719</v>
       </c>
@@ -23637,7 +23919,7 @@
         <v>45694</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>1723</v>
       </c>
@@ -23672,7 +23954,7 @@
         <v>45578</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>1727</v>
       </c>
@@ -23707,7 +23989,7 @@
         <v>44653</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>1732</v>
       </c>
@@ -23742,7 +24024,7 @@
         <v>43551</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>1736</v>
       </c>
@@ -23777,7 +24059,7 @@
         <v>44587</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>1740</v>
       </c>
@@ -23812,7 +24094,7 @@
         <v>44221</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>1744</v>
       </c>
@@ -23847,7 +24129,7 @@
         <v>43606</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>1748</v>
       </c>
@@ -23882,7 +24164,7 @@
         <v>43492</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>1753</v>
       </c>
@@ -23917,7 +24199,7 @@
         <v>44211</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>1757</v>
       </c>
@@ -23952,7 +24234,7 @@
         <v>43841</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>1761</v>
       </c>
@@ -23987,7 +24269,7 @@
         <v>45054</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>1765</v>
       </c>
@@ -24022,7 +24304,7 @@
         <v>45794</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>1769</v>
       </c>
@@ -24057,7 +24339,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>1773</v>
       </c>
@@ -24092,7 +24374,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>1777</v>
       </c>
@@ -24127,7 +24409,7 @@
         <v>44275</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>1781</v>
       </c>
@@ -24162,7 +24444,7 @@
         <v>44352</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>1785</v>
       </c>
@@ -24197,7 +24479,7 @@
         <v>44084</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>1789</v>
       </c>
@@ -24232,7 +24514,7 @@
         <v>45370</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>1793</v>
       </c>
@@ -24267,7 +24549,7 @@
         <v>45874</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>1797</v>
       </c>
@@ -24302,7 +24584,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>1801</v>
       </c>
@@ -24337,7 +24619,7 @@
         <v>46026</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>1805</v>
       </c>
@@ -24372,7 +24654,7 @@
         <v>45902</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>1809</v>
       </c>
@@ -24407,7 +24689,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>1813</v>
       </c>
@@ -24442,7 +24724,7 @@
         <v>44832</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>1817</v>
       </c>
@@ -24477,7 +24759,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>1821</v>
       </c>
@@ -24512,7 +24794,7 @@
         <v>44303</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>1825</v>
       </c>
@@ -24547,7 +24829,7 @@
         <v>45734</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>1829</v>
       </c>
@@ -24582,7 +24864,7 @@
         <v>43336</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>1833</v>
       </c>
@@ -24617,7 +24899,7 @@
         <v>43539</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>1837</v>
       </c>
@@ -24652,7 +24934,7 @@
         <v>43516</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>1841</v>
       </c>
@@ -24685,7 +24967,7 @@
         <v>44783</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>1845</v>
       </c>
@@ -24720,7 +25002,7 @@
         <v>44027</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>1849</v>
       </c>
@@ -24755,7 +25037,7 @@
         <v>45298</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>1853</v>
       </c>
@@ -24790,7 +25072,7 @@
         <v>43763</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>1857</v>
       </c>
@@ -24825,7 +25107,7 @@
         <v>43554</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>1861</v>
       </c>
@@ -24860,7 +25142,7 @@
         <v>43230</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>1865</v>
       </c>
@@ -24895,7 +25177,7 @@
         <v>43587</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>1869</v>
       </c>
@@ -24930,7 +25212,7 @@
         <v>44431</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>1873</v>
       </c>
@@ -24965,7 +25247,7 @@
         <v>43639</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>1877</v>
       </c>
@@ -25000,7 +25282,7 @@
         <v>43156</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>1881</v>
       </c>
@@ -25035,7 +25317,7 @@
         <v>44860</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>1885</v>
       </c>
@@ -25070,7 +25352,7 @@
         <v>45091</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>1889</v>
       </c>
@@ -25105,7 +25387,7 @@
         <v>43866</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>1893</v>
       </c>
@@ -25140,7 +25422,7 @@
         <v>45830</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>1897</v>
       </c>
@@ -25175,7 +25457,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>1901</v>
       </c>
@@ -25210,7 +25492,7 @@
         <v>44040</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>1905</v>
       </c>
@@ -25245,7 +25527,7 @@
         <v>43699</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>1909</v>
       </c>
@@ -25280,7 +25562,7 @@
         <v>44658</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>1913</v>
       </c>
@@ -25315,7 +25597,7 @@
         <v>45063</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>1917</v>
       </c>
@@ -25350,7 +25632,7 @@
         <v>44590</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>1921</v>
       </c>
@@ -25385,7 +25667,7 @@
         <v>43845</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>1925</v>
       </c>
@@ -25420,7 +25702,7 @@
         <v>44248</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>1929</v>
       </c>
@@ -25455,7 +25737,7 @@
         <v>44590</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>1933</v>
       </c>
@@ -25490,7 +25772,7 @@
         <v>43634</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>1937</v>
       </c>
@@ -25525,7 +25807,7 @@
         <v>45267</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>1941</v>
       </c>
@@ -25560,7 +25842,7 @@
         <v>43458</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>1945</v>
       </c>
@@ -25595,7 +25877,7 @@
         <v>45781</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>1949</v>
       </c>
@@ -25630,7 +25912,7 @@
         <v>45339</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>1953</v>
       </c>
@@ -25665,7 +25947,7 @@
         <v>45286</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>1957</v>
       </c>
@@ -25700,7 +25982,7 @@
         <v>46015</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>1961</v>
       </c>
@@ -25735,7 +26017,7 @@
         <v>45680</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>1967</v>
       </c>
@@ -25770,7 +26052,7 @@
         <v>45246</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>1971</v>
       </c>
@@ -25805,7 +26087,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>1975</v>
       </c>
@@ -25840,7 +26122,7 @@
         <v>45128</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>1979</v>
       </c>
@@ -25875,7 +26157,7 @@
         <v>44894</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>1983</v>
       </c>
@@ -25910,7 +26192,7 @@
         <v>45588</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>1987</v>
       </c>
@@ -25945,7 +26227,7 @@
         <v>45526</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>1991</v>
       </c>
@@ -25980,7 +26262,7 @@
         <v>44161</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>1995</v>
       </c>
@@ -26015,7 +26297,7 @@
         <v>44018</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>1999</v>
       </c>
@@ -26050,7 +26332,7 @@
         <v>44238</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>2003</v>
       </c>
@@ -26085,7 +26367,7 @@
         <v>43961</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>2007</v>
       </c>
@@ -26120,7 +26402,7 @@
         <v>44430</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>2011</v>
       </c>
@@ -26155,7 +26437,7 @@
         <v>45605</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>2015</v>
       </c>
@@ -26190,7 +26472,7 @@
         <v>44557</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>2019</v>
       </c>
@@ -26225,7 +26507,7 @@
         <v>45302</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>2023</v>
       </c>
@@ -26260,7 +26542,7 @@
         <v>45779</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>2027</v>
       </c>
@@ -26295,7 +26577,7 @@
         <v>44429</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>2031</v>
       </c>
@@ -26330,7 +26612,7 @@
         <v>46075</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>2035</v>
       </c>
@@ -26365,7 +26647,7 @@
         <v>44982</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>2039</v>
       </c>
@@ -26400,7 +26682,7 @@
         <v>43839</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>2043</v>
       </c>
@@ -26435,7 +26717,7 @@
         <v>44715</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>2047</v>
       </c>
@@ -26470,7 +26752,7 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>2051</v>
       </c>
@@ -26505,7 +26787,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>2055</v>
       </c>
@@ -26540,7 +26822,7 @@
         <v>43185</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>2059</v>
       </c>
@@ -26575,7 +26857,7 @@
         <v>44197</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>2063</v>
       </c>
@@ -26610,7 +26892,7 @@
         <v>43536</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>2067</v>
       </c>
@@ -26645,7 +26927,7 @@
         <v>43929</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>2071</v>
       </c>
@@ -26680,7 +26962,7 @@
         <v>44360</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>2075</v>
       </c>
@@ -26715,7 +26997,7 @@
         <v>45671</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>2079</v>
       </c>
@@ -26750,7 +27032,7 @@
         <v>43521</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>2083</v>
       </c>
@@ -26785,7 +27067,7 @@
         <v>43199</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>2087</v>
       </c>
@@ -26820,7 +27102,7 @@
         <v>44026</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>2091</v>
       </c>
@@ -26855,7 +27137,7 @@
         <v>44020</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>2095</v>
       </c>
@@ -26890,7 +27172,7 @@
         <v>43585</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>2099</v>
       </c>
@@ -26925,7 +27207,7 @@
         <v>44856</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>2103</v>
       </c>
@@ -26960,7 +27242,7 @@
         <v>45834</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>2107</v>
       </c>
@@ -26995,7 +27277,7 @@
         <v>44211</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>2111</v>
       </c>
@@ -27030,7 +27312,7 @@
         <v>43109</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>2115</v>
       </c>
@@ -27065,7 +27347,7 @@
         <v>44930</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>2119</v>
       </c>
@@ -27100,7 +27382,7 @@
         <v>45467</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>2123</v>
       </c>
@@ -27135,7 +27417,7 @@
         <v>43845</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>2127</v>
       </c>
@@ -27170,7 +27452,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>2131</v>
       </c>
@@ -27205,7 +27487,7 @@
         <v>44670</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>2135</v>
       </c>
@@ -27240,7 +27522,7 @@
         <v>45297</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>2139</v>
       </c>
@@ -27275,7 +27557,7 @@
         <v>45259</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>2143</v>
       </c>
@@ -27310,7 +27592,7 @@
         <v>44582</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>2147</v>
       </c>
@@ -27345,7 +27627,7 @@
         <v>43648</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>2151</v>
       </c>
@@ -27380,7 +27662,7 @@
         <v>44308</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>2155</v>
       </c>
@@ -27415,7 +27697,7 @@
         <v>44094</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>2159</v>
       </c>
@@ -27450,7 +27732,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>2163</v>
       </c>
@@ -27483,7 +27765,7 @@
         <v>44623</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>2167</v>
       </c>
@@ -27518,7 +27800,7 @@
         <v>43224</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>2171</v>
       </c>
@@ -27553,7 +27835,7 @@
         <v>45432</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>2175</v>
       </c>
@@ -27588,7 +27870,7 @@
         <v>43674</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>2179</v>
       </c>
@@ -27623,7 +27905,7 @@
         <v>44919</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>2183</v>
       </c>
@@ -27658,7 +27940,7 @@
         <v>43346</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>2187</v>
       </c>
@@ -27693,7 +27975,7 @@
         <v>44724</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>2191</v>
       </c>
@@ -27728,7 +28010,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>2195</v>
       </c>
@@ -27763,7 +28045,7 @@
         <v>44214</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>2199</v>
       </c>
@@ -27798,7 +28080,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>2203</v>
       </c>
@@ -27833,7 +28115,7 @@
         <v>45579</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>2207</v>
       </c>
@@ -27868,7 +28150,7 @@
         <v>44659</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>2211</v>
       </c>
@@ -27903,7 +28185,7 @@
         <v>44206</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>2215</v>
       </c>
@@ -27938,7 +28220,7 @@
         <v>43215</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>2219</v>
       </c>
@@ -27973,7 +28255,7 @@
         <v>45546</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>2223</v>
       </c>
@@ -28008,7 +28290,7 @@
         <v>45715</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>2227</v>
       </c>
@@ -28043,7 +28325,7 @@
         <v>43284</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>2231</v>
       </c>
@@ -28078,7 +28360,7 @@
         <v>44365</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>2235</v>
       </c>
@@ -28113,7 +28395,7 @@
         <v>44701</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>2239</v>
       </c>
@@ -28148,7 +28430,7 @@
         <v>44458</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>2243</v>
       </c>
@@ -28183,7 +28465,7 @@
         <v>43198</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>2247</v>
       </c>
@@ -28218,7 +28500,7 @@
         <v>44289</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>2251</v>
       </c>
@@ -28253,7 +28535,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>2255</v>
       </c>
@@ -28288,7 +28570,7 @@
         <v>45155</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>2259</v>
       </c>
@@ -28323,7 +28605,7 @@
         <v>44489</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>2263</v>
       </c>
@@ -28358,7 +28640,7 @@
         <v>44080</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>2267</v>
       </c>
@@ -28393,7 +28675,7 @@
         <v>45672</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>2271</v>
       </c>
@@ -28428,7 +28710,7 @@
         <v>45342</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>2275</v>
       </c>
@@ -28463,7 +28745,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>2279</v>
       </c>
@@ -28498,7 +28780,7 @@
         <v>44548</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>2283</v>
       </c>
@@ -28533,7 +28815,7 @@
         <v>44149</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>2287</v>
       </c>
@@ -28568,7 +28850,7 @@
         <v>45100</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>2291</v>
       </c>
@@ -28603,7 +28885,7 @@
         <v>44906</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>2295</v>
       </c>
@@ -28638,7 +28920,7 @@
         <v>43442</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>2299</v>
       </c>
@@ -28673,7 +28955,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>2303</v>
       </c>
@@ -28708,7 +28990,7 @@
         <v>43133</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>2307</v>
       </c>
@@ -28743,7 +29025,7 @@
         <v>43399</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>2311</v>
       </c>
@@ -28778,7 +29060,7 @@
         <v>45009</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>2315</v>
       </c>
@@ -28813,7 +29095,7 @@
         <v>43544</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>2319</v>
       </c>
@@ -28848,7 +29130,7 @@
         <v>44400</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>2323</v>
       </c>
@@ -28883,7 +29165,7 @@
         <v>43569</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>2327</v>
       </c>
@@ -28918,7 +29200,7 @@
         <v>43697</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>2331</v>
       </c>
@@ -28953,7 +29235,7 @@
         <v>43356</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>2335</v>
       </c>
@@ -28988,7 +29270,7 @@
         <v>43322</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>2339</v>
       </c>
@@ -29023,7 +29305,7 @@
         <v>43443</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>2343</v>
       </c>
@@ -29058,7 +29340,7 @@
         <v>44820</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>2347</v>
       </c>
@@ -29093,7 +29375,7 @@
         <v>43479</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>2351</v>
       </c>
@@ -29128,7 +29410,7 @@
         <v>44817</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>2356</v>
       </c>
@@ -29163,7 +29445,7 @@
         <v>44553</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>2360</v>
       </c>
@@ -29198,7 +29480,7 @@
         <v>43419</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>2364</v>
       </c>
@@ -29231,7 +29513,7 @@
         <v>43159</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>2368</v>
       </c>
@@ -29266,7 +29548,7 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>2372</v>
       </c>
@@ -29301,7 +29583,7 @@
         <v>45699</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>2376</v>
       </c>
@@ -29336,7 +29618,7 @@
         <v>43869</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>2380</v>
       </c>
@@ -29371,7 +29653,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>2384</v>
       </c>
@@ -29406,7 +29688,7 @@
         <v>43167</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>2388</v>
       </c>
@@ -29441,7 +29723,7 @@
         <v>44796</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>2392</v>
       </c>
@@ -29474,7 +29756,7 @@
         <v>43565</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>2396</v>
       </c>
@@ -29509,7 +29791,7 @@
         <v>45324</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>2400</v>
       </c>
@@ -29544,7 +29826,7 @@
         <v>43459</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>2404</v>
       </c>
@@ -29579,7 +29861,7 @@
         <v>43525</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>2408</v>
       </c>
@@ -29614,7 +29896,7 @@
         <v>45695</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>2412</v>
       </c>
@@ -29649,7 +29931,7 @@
         <v>43968</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>2416</v>
       </c>
@@ -29684,7 +29966,7 @@
         <v>45024</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>2420</v>
       </c>
@@ -29719,7 +30001,7 @@
         <v>43132</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>2424</v>
       </c>
@@ -29754,7 +30036,7 @@
         <v>44360</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>2428</v>
       </c>
@@ -29789,7 +30071,7 @@
         <v>43234</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>2432</v>
       </c>
@@ -29824,7 +30106,7 @@
         <v>45558</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>2436</v>
       </c>
@@ -29859,7 +30141,7 @@
         <v>45377</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>2440</v>
       </c>
@@ -29894,7 +30176,7 @@
         <v>44858</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>2444</v>
       </c>
@@ -29929,7 +30211,7 @@
         <v>45219</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>2448</v>
       </c>
@@ -29964,7 +30246,7 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>2452</v>
       </c>
@@ -29999,7 +30281,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>2456</v>
       </c>
@@ -30034,7 +30316,7 @@
         <v>43148</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>2460</v>
       </c>
@@ -30069,7 +30351,7 @@
         <v>43423</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>2464</v>
       </c>
@@ -30104,7 +30386,7 @@
         <v>43865</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>2468</v>
       </c>
@@ -30139,7 +30421,7 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>2472</v>
       </c>
@@ -30174,7 +30456,7 @@
         <v>44227</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>2476</v>
       </c>
@@ -30209,7 +30491,7 @@
         <v>43524</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>2480</v>
       </c>
@@ -30244,7 +30526,7 @@
         <v>44257</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>2484</v>
       </c>
@@ -30279,7 +30561,7 @@
         <v>43952</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>2488</v>
       </c>
@@ -30314,7 +30596,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>2492</v>
       </c>
@@ -30349,7 +30631,7 @@
         <v>45696</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>2496</v>
       </c>
@@ -30384,7 +30666,7 @@
         <v>45802</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>2500</v>
       </c>
@@ -30419,7 +30701,7 @@
         <v>44521</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>2504</v>
       </c>
@@ -30454,7 +30736,7 @@
         <v>43599</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>2508</v>
       </c>
@@ -30489,7 +30771,7 @@
         <v>43725</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>2512</v>
       </c>
@@ -30524,7 +30806,7 @@
         <v>44001</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>2516</v>
       </c>
@@ -30559,7 +30841,7 @@
         <v>43917</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>2520</v>
       </c>
@@ -30594,7 +30876,7 @@
         <v>45131</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>2524</v>
       </c>
@@ -30629,7 +30911,7 @@
         <v>43809</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>2528</v>
       </c>
@@ -30664,7 +30946,7 @@
         <v>45491</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>2533</v>
       </c>
@@ -30699,7 +30981,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>2537</v>
       </c>
@@ -30734,7 +31016,7 @@
         <v>44406</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>2541</v>
       </c>
@@ -30769,7 +31051,7 @@
         <v>44546</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>2545</v>
       </c>
@@ -30804,7 +31086,7 @@
         <v>45195</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>2549</v>
       </c>
@@ -30839,7 +31121,7 @@
         <v>44543</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>2553</v>
       </c>
@@ -30874,7 +31156,7 @@
         <v>43862</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>2557</v>
       </c>
@@ -30909,7 +31191,7 @@
         <v>43695</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>2561</v>
       </c>
@@ -30944,7 +31226,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>2565</v>
       </c>
@@ -30979,7 +31261,7 @@
         <v>45401</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>2569</v>
       </c>
@@ -31014,7 +31296,7 @@
         <v>43522</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>2573</v>
       </c>
@@ -31049,7 +31331,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>2577</v>
       </c>
@@ -31084,7 +31366,7 @@
         <v>43912</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>2581</v>
       </c>
@@ -31119,7 +31401,7 @@
         <v>44826</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>2585</v>
       </c>
@@ -31154,7 +31436,7 @@
         <v>44069</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>2589</v>
       </c>
@@ -31189,7 +31471,7 @@
         <v>43120</v>
       </c>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>2593</v>
       </c>
@@ -31224,7 +31506,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>2597</v>
       </c>
@@ -31259,7 +31541,7 @@
         <v>44801</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>2602</v>
       </c>
@@ -31294,7 +31576,7 @@
         <v>43427</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>2607</v>
       </c>
@@ -31329,7 +31611,7 @@
         <v>44323</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>2611</v>
       </c>
@@ -31364,7 +31646,7 @@
         <v>43220</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>2615</v>
       </c>
@@ -31399,7 +31681,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>2619</v>
       </c>
@@ -31434,7 +31716,7 @@
         <v>45302</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>2623</v>
       </c>
@@ -31469,7 +31751,7 @@
         <v>43554</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>2627</v>
       </c>
@@ -31504,7 +31786,7 @@
         <v>44206</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>2631</v>
       </c>
@@ -31539,7 +31821,7 @@
         <v>43618</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>2635</v>
       </c>
@@ -31574,7 +31856,7 @@
         <v>45238</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>2639</v>
       </c>
@@ -31609,7 +31891,7 @@
         <v>44419</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>2643</v>
       </c>
@@ -31644,7 +31926,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>2647</v>
       </c>
@@ -31679,7 +31961,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>2651</v>
       </c>
@@ -31714,7 +31996,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>2655</v>
       </c>
@@ -31749,7 +32031,7 @@
         <v>44495</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>2659</v>
       </c>
@@ -31784,7 +32066,7 @@
         <v>44378</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>2663</v>
       </c>
@@ -31819,7 +32101,7 @@
         <v>43633</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>2667</v>
       </c>
@@ -31854,7 +32136,7 @@
         <v>43932</v>
       </c>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>2671</v>
       </c>
@@ -31889,7 +32171,7 @@
         <v>45911</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>2676</v>
       </c>
@@ -31924,7 +32206,7 @@
         <v>43552</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>2680</v>
       </c>
@@ -31959,7 +32241,7 @@
         <v>45051</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>2684</v>
       </c>
@@ -31994,7 +32276,7 @@
         <v>43445</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>2688</v>
       </c>
@@ -32029,7 +32311,7 @@
         <v>45181</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>2692</v>
       </c>
@@ -32064,7 +32346,7 @@
         <v>45757</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>2696</v>
       </c>
@@ -32099,11 +32381,13 @@
         <v>44750</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>2701</v>
       </c>
-      <c r="B660" s="2"/>
+      <c r="B660" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C660" s="2" t="s">
         <v>33</v>
       </c>
@@ -32132,7 +32416,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>2704</v>
       </c>
@@ -32167,7 +32451,7 @@
         <v>43572</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>2708</v>
       </c>
@@ -32202,7 +32486,7 @@
         <v>43514</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>2712</v>
       </c>
@@ -32237,7 +32521,7 @@
         <v>44706</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>2716</v>
       </c>
@@ -32272,7 +32556,7 @@
         <v>43934</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>2720</v>
       </c>
@@ -32307,7 +32591,7 @@
         <v>43487</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>2724</v>
       </c>
@@ -32342,7 +32626,7 @@
         <v>45918</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>2728</v>
       </c>
@@ -32377,7 +32661,7 @@
         <v>44965</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>2732</v>
       </c>
@@ -32412,7 +32696,7 @@
         <v>43828</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>2736</v>
       </c>
@@ -32447,7 +32731,7 @@
         <v>45489</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>2740</v>
       </c>
@@ -32482,7 +32766,7 @@
         <v>43172</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>2744</v>
       </c>
@@ -32517,7 +32801,7 @@
         <v>45161</v>
       </c>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>2749</v>
       </c>
@@ -32552,7 +32836,7 @@
         <v>44954</v>
       </c>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>2753</v>
       </c>
@@ -32587,7 +32871,7 @@
         <v>44139</v>
       </c>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>2757</v>
       </c>
@@ -32622,7 +32906,7 @@
         <v>45222</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>2761</v>
       </c>
@@ -32657,7 +32941,7 @@
         <v>45909</v>
       </c>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>2765</v>
       </c>
@@ -32692,7 +32976,7 @@
         <v>44003</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>2769</v>
       </c>
@@ -32727,7 +33011,7 @@
         <v>45951</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>2773</v>
       </c>
@@ -32762,7 +33046,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>2777</v>
       </c>
@@ -32797,7 +33081,7 @@
         <v>43817</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>2781</v>
       </c>
@@ -32832,7 +33116,7 @@
         <v>44232</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>2785</v>
       </c>
@@ -32867,7 +33151,7 @@
         <v>45609</v>
       </c>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>2789</v>
       </c>
@@ -32902,7 +33186,7 @@
         <v>44282</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>2793</v>
       </c>
@@ -32937,7 +33221,7 @@
         <v>45243</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>2797</v>
       </c>
@@ -32972,11 +33256,13 @@
         <v>43365</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>2801</v>
       </c>
-      <c r="B685" s="2"/>
+      <c r="B685" s="2" t="s">
+        <v>2869</v>
+      </c>
       <c r="C685" s="2" t="s">
         <v>13</v>
       </c>
@@ -33005,7 +33291,7 @@
         <v>45530</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>2804</v>
       </c>
@@ -33040,7 +33326,7 @@
         <v>45805</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>2808</v>
       </c>
@@ -33075,7 +33361,7 @@
         <v>45157</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>2812</v>
       </c>
@@ -33110,7 +33396,7 @@
         <v>43685</v>
       </c>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>2816</v>
       </c>
@@ -33145,7 +33431,7 @@
         <v>43997</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>2820</v>
       </c>
@@ -33180,7 +33466,7 @@
         <v>44831</v>
       </c>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>2824</v>
       </c>
@@ -33215,7 +33501,7 @@
         <v>43810</v>
       </c>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>2828</v>
       </c>
@@ -33250,7 +33536,7 @@
         <v>45899</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>2832</v>
       </c>
@@ -33285,7 +33571,7 @@
         <v>44334</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>2836</v>
       </c>
@@ -33320,7 +33606,7 @@
         <v>45336</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>2840</v>
       </c>
@@ -33355,7 +33641,7 @@
         <v>44911</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>2844</v>
       </c>
@@ -33390,7 +33676,7 @@
         <v>45011</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>2848</v>
       </c>
@@ -33425,7 +33711,7 @@
         <v>44825</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>2853</v>
       </c>
@@ -33460,7 +33746,7 @@
         <v>45478</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>2857</v>
       </c>
@@ -33495,7 +33781,7 @@
         <v>44302</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>2861</v>
       </c>
@@ -33530,7 +33816,7 @@
         <v>44996</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>2865</v>
       </c>
@@ -33563,6 +33849,29 @@
       </c>
       <c r="K701" s="3">
         <v>43447</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BDD43C7-421C-4B67-A06A-FF8CA8423FDE}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
